--- a/output/graficos_regionales/plot_regional_serie_i_ingr_median_m_2023_los_rios.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_median_m_2023_los_rios.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:48</t>
+    <t xml:space="preserve">2026-10-05 02:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -998,7 +998,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>556567.12</v>
+        <v>556567.13</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>615210</v>
